--- a/hardware/boards/handgrip/PickAndPlace_handgrip.xlsx
+++ b/hardware/boards/handgrip/PickAndPlace_handgrip.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB1_2026_07_20" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_handgrip_2026_09_1" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="223">
   <si>
     <t>Designator</t>
   </si>
@@ -145,9 +145,6 @@
     <t>-20.599mm</t>
   </si>
   <si>
-    <t>JP7</t>
-  </si>
-  <si>
     <t>KEY1</t>
   </si>
   <si>
@@ -298,18 +295,6 @@
     <t>10kΩ</t>
   </si>
   <si>
-    <t>R41</t>
-  </si>
-  <si>
-    <t>86.995mm</t>
-  </si>
-  <si>
-    <t>-12.827mm</t>
-  </si>
-  <si>
-    <t>-12.394mm</t>
-  </si>
-  <si>
     <t>U4</t>
   </si>
   <si>
@@ -412,7 +397,7 @@
     <t>58.25mm</t>
   </si>
   <si>
-    <t>TP1</t>
+    <t>5V</t>
   </si>
   <si>
     <t>Test-Point</t>
@@ -421,120 +406,6 @@
     <t>Test-Point-0.5mm</t>
   </si>
   <si>
-    <t>73.843mm</t>
-  </si>
-  <si>
-    <t>-4.742mm</t>
-  </si>
-  <si>
-    <t>TP2</t>
-  </si>
-  <si>
-    <t>59.27mm</t>
-  </si>
-  <si>
-    <t>-5.123mm</t>
-  </si>
-  <si>
-    <t>TP3</t>
-  </si>
-  <si>
-    <t>95.766mm</t>
-  </si>
-  <si>
-    <t>-4.488mm</t>
-  </si>
-  <si>
-    <t>TP4</t>
-  </si>
-  <si>
-    <t>108.704mm</t>
-  </si>
-  <si>
-    <t>TP5</t>
-  </si>
-  <si>
-    <t>113.736mm</t>
-  </si>
-  <si>
-    <t>-18.68mm</t>
-  </si>
-  <si>
-    <t>TP6</t>
-  </si>
-  <si>
-    <t>125.944mm</t>
-  </si>
-  <si>
-    <t>-16.997mm</t>
-  </si>
-  <si>
-    <t>TP7</t>
-  </si>
-  <si>
-    <t>94.337mm</t>
-  </si>
-  <si>
-    <t>-53.922mm</t>
-  </si>
-  <si>
-    <t>TP8</t>
-  </si>
-  <si>
-    <t>74.208mm</t>
-  </si>
-  <si>
-    <t>-51.763mm</t>
-  </si>
-  <si>
-    <t>TP9</t>
-  </si>
-  <si>
-    <t>74.494mm</t>
-  </si>
-  <si>
-    <t>-31.697mm</t>
-  </si>
-  <si>
-    <t>TP10</t>
-  </si>
-  <si>
-    <t>74.462mm</t>
-  </si>
-  <si>
-    <t>-71.813mm</t>
-  </si>
-  <si>
-    <t>TP11</t>
-  </si>
-  <si>
-    <t>42.284mm</t>
-  </si>
-  <si>
-    <t>-16.664mm</t>
-  </si>
-  <si>
-    <t>TP12</t>
-  </si>
-  <si>
-    <t>50.523mm</t>
-  </si>
-  <si>
-    <t>-17.775mm</t>
-  </si>
-  <si>
-    <t>TP13</t>
-  </si>
-  <si>
-    <t>70.001mm</t>
-  </si>
-  <si>
-    <t>-51.271mm</t>
-  </si>
-  <si>
-    <t>5V</t>
-  </si>
-  <si>
     <t>75.796mm</t>
   </si>
   <si>
@@ -545,6 +416,270 @@
   </si>
   <si>
     <t>-7.536mm</t>
+  </si>
+  <si>
+    <t>H7</t>
+  </si>
+  <si>
+    <t>PZ2.54-1x3PZZ-L11.5</t>
+  </si>
+  <si>
+    <t>HDR-TH_PZ2.54-1X3PZZ-L11.5</t>
+  </si>
+  <si>
+    <t>100.53mm</t>
+  </si>
+  <si>
+    <t>-27.232mm</t>
+  </si>
+  <si>
+    <t>103.07mm</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>39.878mm</t>
+  </si>
+  <si>
+    <t>-17.018mm</t>
+  </si>
+  <si>
+    <t>39.333mm</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>70.612mm</t>
+  </si>
+  <si>
+    <t>-51.689mm</t>
+  </si>
+  <si>
+    <t>-52.234mm</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>85.598mm</t>
+  </si>
+  <si>
+    <t>-63.119mm</t>
+  </si>
+  <si>
+    <t>86.143mm</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>94.107mm</t>
+  </si>
+  <si>
+    <t>-48.768mm</t>
+  </si>
+  <si>
+    <t>-48.223mm</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>85.217mm</t>
+  </si>
+  <si>
+    <t>-43.434mm</t>
+  </si>
+  <si>
+    <t>85.762mm</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>126.365mm</t>
+  </si>
+  <si>
+    <t>-20.574mm</t>
+  </si>
+  <si>
+    <t>126.91mm</t>
+  </si>
+  <si>
+    <t>LED1</t>
+  </si>
+  <si>
+    <t>SK6805-EC15</t>
+  </si>
+  <si>
+    <t>LED-SMD_4P-L1.5-W1.5-BL</t>
+  </si>
+  <si>
+    <t>41.148mm</t>
+  </si>
+  <si>
+    <t>-18.542mm</t>
+  </si>
+  <si>
+    <t>41.623mm</t>
+  </si>
+  <si>
+    <t>-18.067mm</t>
+  </si>
+  <si>
+    <t>LED2</t>
+  </si>
+  <si>
+    <t>72.263mm</t>
+  </si>
+  <si>
+    <t>72.738mm</t>
+  </si>
+  <si>
+    <t>-51.214mm</t>
+  </si>
+  <si>
+    <t>LED3</t>
+  </si>
+  <si>
+    <t>82.677mm</t>
+  </si>
+  <si>
+    <t>-62.611mm</t>
+  </si>
+  <si>
+    <t>82.202mm</t>
+  </si>
+  <si>
+    <t>-63.086mm</t>
+  </si>
+  <si>
+    <t>LED4</t>
+  </si>
+  <si>
+    <t>92.583mm</t>
+  </si>
+  <si>
+    <t>-51.562mm</t>
+  </si>
+  <si>
+    <t>92.108mm</t>
+  </si>
+  <si>
+    <t>-52.037mm</t>
+  </si>
+  <si>
+    <t>LED5</t>
+  </si>
+  <si>
+    <t>82.804mm</t>
+  </si>
+  <si>
+    <t>-42.164mm</t>
+  </si>
+  <si>
+    <t>82.329mm</t>
+  </si>
+  <si>
+    <t>-42.639mm</t>
+  </si>
+  <si>
+    <t>LED6</t>
+  </si>
+  <si>
+    <t>124.587mm</t>
+  </si>
+  <si>
+    <t>-18.669mm</t>
+  </si>
+  <si>
+    <t>124.112mm</t>
+  </si>
+  <si>
+    <t>-19.144mm</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>78.486mm</t>
+  </si>
+  <si>
+    <t>-4.191mm</t>
+  </si>
+  <si>
+    <t>-3.646mm</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>60.421mm</t>
+  </si>
+  <si>
+    <t>-4.868mm</t>
+  </si>
+  <si>
+    <t>-4.323mm</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>97.536mm</t>
+  </si>
+  <si>
+    <t>-4.826mm</t>
+  </si>
+  <si>
+    <t>-5.371mm</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>SK6805SIDE-G-003</t>
+  </si>
+  <si>
+    <t>LED-SMD_4P-L3.5-W1.6_SK6805SIDE-G-001</t>
+  </si>
+  <si>
+    <t>100.33mm</t>
+  </si>
+  <si>
+    <t>-4.445mm</t>
+  </si>
+  <si>
+    <t>101.995mm</t>
+  </si>
+  <si>
+    <t>-4.51mm</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>81.407mm</t>
+  </si>
+  <si>
+    <t>-4.572mm</t>
+  </si>
+  <si>
+    <t>83.072mm</t>
+  </si>
+  <si>
+    <t>-4.637mm</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>63.246mm</t>
+  </si>
+  <si>
+    <t>64.911mm</t>
   </si>
 </sst>
 </file>
@@ -921,7 +1056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="15" width="20" customWidth="1"/>
@@ -1167,75 +1302,75 @@
         <v>44</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="F6" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="G6" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="I6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K6" t="s">
         <v>21</v>
       </c>
       <c r="L6">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M6" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="N6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="O6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
         <v>45</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>46</v>
       </c>
-      <c r="C7" t="s">
-        <v>47</v>
-      </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F7" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H7" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I7" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J7">
         <v>4</v>
@@ -1250,39 +1385,39 @@
         <v>37</v>
       </c>
       <c r="N7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="s">
         <v>46</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>47</v>
       </c>
-      <c r="D8" t="s">
-        <v>54</v>
-      </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F8" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="G8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H8" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="I8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J8">
         <v>4</v>
@@ -1297,39 +1432,39 @@
         <v>37</v>
       </c>
       <c r="N8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" t="s">
         <v>46</v>
       </c>
-      <c r="C9" t="s">
-        <v>47</v>
-      </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G9" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H9" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="I9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J9">
         <v>4</v>
@@ -1338,45 +1473,45 @@
         <v>21</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M9" t="s">
         <v>37</v>
       </c>
       <c r="N9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
         <v>46</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>47</v>
       </c>
-      <c r="D10" t="s">
-        <v>62</v>
-      </c>
       <c r="E10" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="G10" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H10" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="I10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J10">
         <v>4</v>
@@ -1385,45 +1520,45 @@
         <v>21</v>
       </c>
       <c r="L10">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M10" t="s">
         <v>37</v>
       </c>
       <c r="N10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" t="s">
         <v>46</v>
       </c>
-      <c r="C11" t="s">
-        <v>47</v>
-      </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F11" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="G11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H11" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="I11" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="J11">
         <v>4</v>
@@ -1432,45 +1567,45 @@
         <v>21</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="M11" t="s">
         <v>37</v>
       </c>
       <c r="N11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
         <v>46</v>
       </c>
-      <c r="C12" t="s">
-        <v>47</v>
-      </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H12" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="J12">
         <v>4</v>
@@ -1479,45 +1614,45 @@
         <v>21</v>
       </c>
       <c r="L12">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="M12" t="s">
         <v>37</v>
       </c>
       <c r="N12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O12" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
         <v>46</v>
       </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="J13">
         <v>4</v>
@@ -1526,45 +1661,45 @@
         <v>21</v>
       </c>
       <c r="L13">
-        <v>45</v>
+        <v>135</v>
       </c>
       <c r="M13" t="s">
         <v>37</v>
       </c>
       <c r="N13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
         <v>46</v>
       </c>
-      <c r="C14" t="s">
-        <v>47</v>
-      </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I14" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="J14">
         <v>4</v>
@@ -1573,327 +1708,327 @@
         <v>21</v>
       </c>
       <c r="L14">
-        <v>135</v>
+        <v>315</v>
       </c>
       <c r="M14" t="s">
         <v>37</v>
       </c>
       <c r="N14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="O14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="F15" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G15" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I15" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K15" t="s">
         <v>21</v>
       </c>
       <c r="L15">
-        <v>315</v>
+        <v>0</v>
       </c>
       <c r="M15" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="N15" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="O15" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="F16" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G16" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H16" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="I16" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="J16">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="K16" t="s">
         <v>21</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M16" t="s">
         <v>22</v>
       </c>
       <c r="N16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D17" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E17" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F17" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="G17" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="H17" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="I17" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="J17">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K17" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="L17">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M17" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="N17" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="O17" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F18" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G18" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="H18" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="I18" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J18">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="K18" t="s">
-        <v>21</v>
+        <v>107</v>
       </c>
       <c r="L18">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M18" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="N18" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="O18" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F19" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="G19" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="H19" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="I19" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="J19">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K19" t="s">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M19" t="s">
         <v>37</v>
       </c>
       <c r="N19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="O19" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" t="s">
         <v>113</v>
       </c>
-      <c r="B20" t="s">
-        <v>32</v>
-      </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F20" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G20" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H20" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="I20" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="J20">
         <v>4</v>
       </c>
       <c r="K20" t="s">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M20" t="s">
         <v>37</v>
       </c>
       <c r="N20" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
       <c r="O20" t="s">
-        <v>32</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B21" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" t="s">
+        <v>123</v>
+      </c>
+      <c r="G21" t="s">
+        <v>116</v>
+      </c>
+      <c r="H21" t="s">
+        <v>124</v>
+      </c>
+      <c r="I21" t="s">
         <v>118</v>
-      </c>
-      <c r="C21" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" t="s">
-        <v>120</v>
-      </c>
-      <c r="E21" t="s">
-        <v>121</v>
-      </c>
-      <c r="F21" t="s">
-        <v>120</v>
-      </c>
-      <c r="G21" t="s">
-        <v>121</v>
-      </c>
-      <c r="H21" t="s">
-        <v>122</v>
-      </c>
-      <c r="I21" t="s">
-        <v>123</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -1908,39 +2043,39 @@
         <v>37</v>
       </c>
       <c r="N21" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="O21" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B22" t="s">
+        <v>113</v>
+      </c>
+      <c r="C22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" t="s">
+        <v>126</v>
+      </c>
+      <c r="E22" t="s">
+        <v>116</v>
+      </c>
+      <c r="F22" t="s">
+        <v>126</v>
+      </c>
+      <c r="G22" t="s">
+        <v>116</v>
+      </c>
+      <c r="H22" t="s">
+        <v>127</v>
+      </c>
+      <c r="I22" t="s">
         <v>118</v>
-      </c>
-      <c r="C22" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" t="s">
-        <v>121</v>
-      </c>
-      <c r="F22" t="s">
-        <v>125</v>
-      </c>
-      <c r="G22" t="s">
-        <v>121</v>
-      </c>
-      <c r="H22" t="s">
-        <v>126</v>
-      </c>
-      <c r="I22" t="s">
-        <v>123</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -1955,183 +2090,183 @@
         <v>37</v>
       </c>
       <c r="N22" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="O22" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D23" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E23" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F23" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G23" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="H23" t="s">
+        <v>131</v>
+      </c>
+      <c r="I23" t="s">
+        <v>132</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" t="s">
         <v>129</v>
       </c>
-      <c r="I23" t="s">
-        <v>123</v>
-      </c>
-      <c r="J23">
-        <v>4</v>
-      </c>
-      <c r="K23" t="s">
-        <v>21</v>
-      </c>
-      <c r="L23">
-        <v>180</v>
-      </c>
-      <c r="M23" t="s">
-        <v>37</v>
-      </c>
-      <c r="N23" t="s">
-        <v>118</v>
-      </c>
       <c r="O23" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" t="s">
+        <v>129</v>
+      </c>
+      <c r="C24" t="s">
         <v>130</v>
       </c>
-      <c r="B24" t="s">
-        <v>118</v>
-      </c>
-      <c r="C24" t="s">
-        <v>119</v>
-      </c>
       <c r="D24" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E24" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="F24" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="H24" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I24" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="J24">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K24" t="s">
         <v>21</v>
       </c>
       <c r="L24">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M24" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="N24" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="O24" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B25" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C25" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D25" t="s">
+        <v>138</v>
+      </c>
+      <c r="E25" t="s">
+        <v>139</v>
+      </c>
+      <c r="F25" t="s">
+        <v>138</v>
+      </c>
+      <c r="G25" t="s">
+        <v>139</v>
+      </c>
+      <c r="H25" t="s">
+        <v>140</v>
+      </c>
+      <c r="I25" t="s">
+        <v>139</v>
+      </c>
+      <c r="J25">
+        <v>3</v>
+      </c>
+      <c r="K25" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25">
+        <v>180</v>
+      </c>
+      <c r="M25" t="s">
+        <v>37</v>
+      </c>
+      <c r="N25" t="s">
         <v>136</v>
       </c>
-      <c r="E25" t="s">
-        <v>137</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="O25" t="s">
         <v>136</v>
-      </c>
-      <c r="G25" t="s">
-        <v>137</v>
-      </c>
-      <c r="H25" t="s">
-        <v>136</v>
-      </c>
-      <c r="I25" t="s">
-        <v>137</v>
-      </c>
-      <c r="J25">
-        <v>1</v>
-      </c>
-      <c r="K25" t="s">
-        <v>21</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25" t="s">
-        <v>22</v>
-      </c>
-      <c r="N25" t="s">
-        <v>134</v>
-      </c>
-      <c r="O25" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B26" t="s">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="C26" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E26" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F26" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G26" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="H26" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I26" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" t="s">
         <v>21</v>
@@ -2143,371 +2278,371 @@
         <v>22</v>
       </c>
       <c r="N26" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="O26" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B27" t="s">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="C27" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E27" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F27" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G27" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H27" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I27" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K27" t="s">
         <v>21</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M27" t="s">
         <v>22</v>
       </c>
       <c r="N27" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="O27" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B28" t="s">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="C28" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="D28" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E28" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="F28" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G28" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="H28" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="I28" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K28" t="s">
         <v>21</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M28" t="s">
         <v>22</v>
       </c>
       <c r="N28" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="O28" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="E29" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="F29" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="G29" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="H29" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I29" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" t="s">
         <v>21</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s">
         <v>22</v>
       </c>
       <c r="N29" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="O29" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="B30" t="s">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E30" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="F30" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="G30" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H30" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="I30" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="J30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" t="s">
         <v>21</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M30" t="s">
         <v>22</v>
       </c>
       <c r="N30" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="O30" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B31" t="s">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="E31" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F31" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G31" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="H31" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="I31" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" t="s">
         <v>21</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M31" t="s">
         <v>22</v>
       </c>
       <c r="N31" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="O31" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="C32" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="D32" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="E32" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="F32" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="G32" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="H32" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="I32" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K32" t="s">
         <v>21</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M32" t="s">
         <v>22</v>
       </c>
       <c r="N32" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="O32" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B33" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="C33" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="D33" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="E33" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="F33" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="G33" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="H33" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="I33" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K33" t="s">
         <v>21</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M33" t="s">
         <v>22</v>
       </c>
       <c r="N33" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="O33" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B34" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="C34" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="D34" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="E34" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="F34" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="G34" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="H34" t="s">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="I34" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="J34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K34" t="s">
         <v>21</v>
@@ -2519,42 +2654,42 @@
         <v>22</v>
       </c>
       <c r="N34" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="O34" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="B35" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="C35" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="D35" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="E35" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="F35" t="s">
-        <v>165</v>
+        <v>182</v>
       </c>
       <c r="G35" t="s">
-        <v>166</v>
+        <v>183</v>
       </c>
       <c r="H35" t="s">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="I35" t="s">
-        <v>166</v>
+        <v>185</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K35" t="s">
         <v>21</v>
@@ -2566,42 +2701,42 @@
         <v>22</v>
       </c>
       <c r="N35" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="O35" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>186</v>
+      </c>
+      <c r="B36" t="s">
+        <v>166</v>
+      </c>
+      <c r="C36" t="s">
         <v>167</v>
       </c>
-      <c r="B36" t="s">
-        <v>134</v>
-      </c>
-      <c r="C36" t="s">
-        <v>135</v>
-      </c>
       <c r="D36" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="E36" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="F36" t="s">
-        <v>168</v>
+        <v>187</v>
       </c>
       <c r="G36" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="H36" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="I36" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="J36">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K36" t="s">
         <v>21</v>
@@ -2613,42 +2748,42 @@
         <v>22</v>
       </c>
       <c r="N36" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="O36" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="C37" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
       <c r="D37" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="E37" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="F37" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="G37" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="H37" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="I37" t="s">
-        <v>172</v>
+        <v>195</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K37" t="s">
         <v>21</v>
@@ -2660,104 +2795,292 @@
         <v>22</v>
       </c>
       <c r="N37" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="O37" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="B38" t="s">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="C38" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="D38" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="E38" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="F38" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="G38" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="H38" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="I38" t="s">
-        <v>175</v>
+        <v>199</v>
       </c>
       <c r="J38">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K38" t="s">
         <v>21</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M38" t="s">
         <v>22</v>
       </c>
       <c r="N38" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="O38" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="B39" t="s">
-        <v>134</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="D39" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="E39" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="F39" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="G39" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="H39" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="I39" t="s">
-        <v>177</v>
+        <v>203</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K39" t="s">
         <v>21</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="M39" t="s">
         <v>22</v>
       </c>
       <c r="N39" t="s">
-        <v>134</v>
+        <v>30</v>
       </c>
       <c r="O39" t="s">
-        <v>134</v>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>204</v>
+      </c>
+      <c r="B40" t="s">
+        <v>25</v>
+      </c>
+      <c r="C40" t="s">
+        <v>26</v>
+      </c>
+      <c r="D40" t="s">
+        <v>205</v>
+      </c>
+      <c r="E40" t="s">
+        <v>206</v>
+      </c>
+      <c r="F40" t="s">
+        <v>205</v>
+      </c>
+      <c r="G40" t="s">
+        <v>206</v>
+      </c>
+      <c r="H40" t="s">
+        <v>205</v>
+      </c>
+      <c r="I40" t="s">
+        <v>207</v>
+      </c>
+      <c r="J40">
+        <v>2</v>
+      </c>
+      <c r="K40" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40">
+        <v>90</v>
+      </c>
+      <c r="M40" t="s">
+        <v>22</v>
+      </c>
+      <c r="N40" t="s">
+        <v>30</v>
+      </c>
+      <c r="O40" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>208</v>
+      </c>
+      <c r="B41" t="s">
+        <v>209</v>
+      </c>
+      <c r="C41" t="s">
+        <v>210</v>
+      </c>
+      <c r="D41" t="s">
+        <v>211</v>
+      </c>
+      <c r="E41" t="s">
+        <v>212</v>
+      </c>
+      <c r="F41" t="s">
+        <v>211</v>
+      </c>
+      <c r="G41" t="s">
+        <v>212</v>
+      </c>
+      <c r="H41" t="s">
+        <v>213</v>
+      </c>
+      <c r="I41" t="s">
+        <v>214</v>
+      </c>
+      <c r="J41">
+        <v>4</v>
+      </c>
+      <c r="K41" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41">
+        <v>180</v>
+      </c>
+      <c r="M41" t="s">
+        <v>22</v>
+      </c>
+      <c r="N41" t="s">
+        <v>209</v>
+      </c>
+      <c r="O41" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>215</v>
+      </c>
+      <c r="B42" t="s">
+        <v>209</v>
+      </c>
+      <c r="C42" t="s">
+        <v>210</v>
+      </c>
+      <c r="D42" t="s">
+        <v>216</v>
+      </c>
+      <c r="E42" t="s">
+        <v>217</v>
+      </c>
+      <c r="F42" t="s">
+        <v>216</v>
+      </c>
+      <c r="G42" t="s">
+        <v>217</v>
+      </c>
+      <c r="H42" t="s">
+        <v>218</v>
+      </c>
+      <c r="I42" t="s">
+        <v>219</v>
+      </c>
+      <c r="J42">
+        <v>4</v>
+      </c>
+      <c r="K42" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42">
+        <v>180</v>
+      </c>
+      <c r="M42" t="s">
+        <v>22</v>
+      </c>
+      <c r="N42" t="s">
+        <v>209</v>
+      </c>
+      <c r="O42" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>220</v>
+      </c>
+      <c r="B43" t="s">
+        <v>209</v>
+      </c>
+      <c r="C43" t="s">
+        <v>210</v>
+      </c>
+      <c r="D43" t="s">
+        <v>221</v>
+      </c>
+      <c r="E43" t="s">
+        <v>217</v>
+      </c>
+      <c r="F43" t="s">
+        <v>221</v>
+      </c>
+      <c r="G43" t="s">
+        <v>217</v>
+      </c>
+      <c r="H43" t="s">
+        <v>222</v>
+      </c>
+      <c r="I43" t="s">
+        <v>219</v>
+      </c>
+      <c r="J43">
+        <v>4</v>
+      </c>
+      <c r="K43" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43">
+        <v>180</v>
+      </c>
+      <c r="M43" t="s">
+        <v>22</v>
+      </c>
+      <c r="N43" t="s">
+        <v>209</v>
+      </c>
+      <c r="O43" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>

--- a/hardware/boards/handgrip/PickAndPlace_handgrip.xlsx
+++ b/hardware/boards/handgrip/PickAndPlace_handgrip.xlsx
@@ -508,25 +508,106 @@
     <t>126.91mm</t>
   </si>
   <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>78.486mm</t>
+  </si>
+  <si>
+    <t>-4.191mm</t>
+  </si>
+  <si>
+    <t>-3.646mm</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>60.421mm</t>
+  </si>
+  <si>
+    <t>-4.868mm</t>
+  </si>
+  <si>
+    <t>-4.323mm</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>97.536mm</t>
+  </si>
+  <si>
+    <t>-4.826mm</t>
+  </si>
+  <si>
+    <t>-5.371mm</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>SK6805SIDE-G-003</t>
+  </si>
+  <si>
+    <t>LED-SMD_4P-L3.5-W1.6_SK6805SIDE-G-001</t>
+  </si>
+  <si>
+    <t>100.33mm</t>
+  </si>
+  <si>
+    <t>-4.445mm</t>
+  </si>
+  <si>
+    <t>101.995mm</t>
+  </si>
+  <si>
+    <t>-4.51mm</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>81.407mm</t>
+  </si>
+  <si>
+    <t>-4.572mm</t>
+  </si>
+  <si>
+    <t>83.072mm</t>
+  </si>
+  <si>
+    <t>-4.637mm</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>63.246mm</t>
+  </si>
+  <si>
+    <t>64.911mm</t>
+  </si>
+  <si>
     <t>LED1</t>
   </si>
   <si>
-    <t>SK6805-EC15</t>
-  </si>
-  <si>
-    <t>LED-SMD_4P-L1.5-W1.5-BL</t>
+    <t>SK6805D-EC2018</t>
+  </si>
+  <si>
+    <t>LED-SMD_4P-L2.0-W1.8-BL_SK6805D</t>
   </si>
   <si>
     <t>41.148mm</t>
   </si>
   <si>
-    <t>-18.542mm</t>
-  </si>
-  <si>
-    <t>41.623mm</t>
-  </si>
-  <si>
-    <t>-18.067mm</t>
+    <t>-18.923mm</t>
+  </si>
+  <si>
+    <t>40.548mm</t>
+  </si>
+  <si>
+    <t>-19.573mm</t>
   </si>
   <si>
     <t>LED2</t>
@@ -535,10 +616,10 @@
     <t>72.263mm</t>
   </si>
   <si>
-    <t>72.738mm</t>
-  </si>
-  <si>
-    <t>-51.214mm</t>
+    <t>71.663mm</t>
+  </si>
+  <si>
+    <t>-52.339mm</t>
   </si>
   <si>
     <t>LED3</t>
@@ -550,10 +631,10 @@
     <t>-62.611mm</t>
   </si>
   <si>
-    <t>82.202mm</t>
-  </si>
-  <si>
-    <t>-63.086mm</t>
+    <t>83.277mm</t>
+  </si>
+  <si>
+    <t>-61.961mm</t>
   </si>
   <si>
     <t>LED4</t>
@@ -565,10 +646,10 @@
     <t>-51.562mm</t>
   </si>
   <si>
-    <t>92.108mm</t>
-  </si>
-  <si>
-    <t>-52.037mm</t>
+    <t>93.183mm</t>
+  </si>
+  <si>
+    <t>-50.912mm</t>
   </si>
   <si>
     <t>LED5</t>
@@ -580,10 +661,10 @@
     <t>-42.164mm</t>
   </si>
   <si>
-    <t>82.329mm</t>
-  </si>
-  <si>
-    <t>-42.639mm</t>
+    <t>83.404mm</t>
+  </si>
+  <si>
+    <t>-41.514mm</t>
   </si>
   <si>
     <t>LED6</t>
@@ -595,91 +676,10 @@
     <t>-18.669mm</t>
   </si>
   <si>
-    <t>124.112mm</t>
-  </si>
-  <si>
-    <t>-19.144mm</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>78.486mm</t>
-  </si>
-  <si>
-    <t>-4.191mm</t>
-  </si>
-  <si>
-    <t>-3.646mm</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>60.421mm</t>
-  </si>
-  <si>
-    <t>-4.868mm</t>
-  </si>
-  <si>
-    <t>-4.323mm</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>97.536mm</t>
-  </si>
-  <si>
-    <t>-4.826mm</t>
-  </si>
-  <si>
-    <t>-5.371mm</t>
-  </si>
-  <si>
-    <t>U1</t>
-  </si>
-  <si>
-    <t>SK6805SIDE-G-003</t>
-  </si>
-  <si>
-    <t>LED-SMD_4P-L3.5-W1.6_SK6805SIDE-G-001</t>
-  </si>
-  <si>
-    <t>100.33mm</t>
-  </si>
-  <si>
-    <t>-4.445mm</t>
-  </si>
-  <si>
-    <t>101.995mm</t>
-  </si>
-  <si>
-    <t>-4.51mm</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>81.407mm</t>
-  </si>
-  <si>
-    <t>-4.572mm</t>
-  </si>
-  <si>
-    <t>83.072mm</t>
-  </si>
-  <si>
-    <t>-4.637mm</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>63.246mm</t>
-  </si>
-  <si>
-    <t>64.911mm</t>
+    <t>125.187mm</t>
+  </si>
+  <si>
+    <t>-18.019mm</t>
   </si>
 </sst>
 </file>
@@ -2524,169 +2524,169 @@
         <v>165</v>
       </c>
       <c r="B32" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" t="s">
         <v>166</v>
       </c>
-      <c r="C32" t="s">
+      <c r="E32" t="s">
         <v>167</v>
       </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
+        <v>166</v>
+      </c>
+      <c r="G32" t="s">
+        <v>167</v>
+      </c>
+      <c r="H32" t="s">
+        <v>166</v>
+      </c>
+      <c r="I32" t="s">
         <v>168</v>
       </c>
-      <c r="E32" t="s">
-        <v>169</v>
-      </c>
-      <c r="F32" t="s">
-        <v>168</v>
-      </c>
-      <c r="G32" t="s">
-        <v>169</v>
-      </c>
-      <c r="H32" t="s">
-        <v>170</v>
-      </c>
-      <c r="I32" t="s">
-        <v>171</v>
-      </c>
       <c r="J32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K32" t="s">
         <v>21</v>
       </c>
       <c r="L32">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M32" t="s">
         <v>22</v>
       </c>
       <c r="N32" t="s">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="O32" t="s">
-        <v>166</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>169</v>
+      </c>
+      <c r="B33" t="s">
+        <v>25</v>
+      </c>
+      <c r="C33" t="s">
+        <v>26</v>
+      </c>
+      <c r="D33" t="s">
+        <v>170</v>
+      </c>
+      <c r="E33" t="s">
+        <v>171</v>
+      </c>
+      <c r="F33" t="s">
+        <v>170</v>
+      </c>
+      <c r="G33" t="s">
+        <v>171</v>
+      </c>
+      <c r="H33" t="s">
+        <v>170</v>
+      </c>
+      <c r="I33" t="s">
         <v>172</v>
       </c>
-      <c r="B33" t="s">
-        <v>166</v>
-      </c>
-      <c r="C33" t="s">
-        <v>167</v>
-      </c>
-      <c r="D33" t="s">
-        <v>173</v>
-      </c>
-      <c r="E33" t="s">
-        <v>147</v>
-      </c>
-      <c r="F33" t="s">
-        <v>173</v>
-      </c>
-      <c r="G33" t="s">
-        <v>147</v>
-      </c>
-      <c r="H33" t="s">
-        <v>174</v>
-      </c>
-      <c r="I33" t="s">
-        <v>175</v>
-      </c>
       <c r="J33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K33" t="s">
         <v>21</v>
       </c>
       <c r="L33">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="M33" t="s">
         <v>22</v>
       </c>
       <c r="N33" t="s">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="O33" t="s">
-        <v>166</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>173</v>
+      </c>
+      <c r="B34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C34" t="s">
+        <v>26</v>
+      </c>
+      <c r="D34" t="s">
+        <v>174</v>
+      </c>
+      <c r="E34" t="s">
+        <v>175</v>
+      </c>
+      <c r="F34" t="s">
+        <v>174</v>
+      </c>
+      <c r="G34" t="s">
+        <v>175</v>
+      </c>
+      <c r="H34" t="s">
+        <v>174</v>
+      </c>
+      <c r="I34" t="s">
         <v>176</v>
       </c>
-      <c r="B34" t="s">
-        <v>166</v>
-      </c>
-      <c r="C34" t="s">
-        <v>167</v>
-      </c>
-      <c r="D34" t="s">
-        <v>177</v>
-      </c>
-      <c r="E34" t="s">
-        <v>178</v>
-      </c>
-      <c r="F34" t="s">
-        <v>177</v>
-      </c>
-      <c r="G34" t="s">
-        <v>178</v>
-      </c>
-      <c r="H34" t="s">
-        <v>179</v>
-      </c>
-      <c r="I34" t="s">
-        <v>180</v>
-      </c>
       <c r="J34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K34" t="s">
         <v>21</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M34" t="s">
         <v>22</v>
       </c>
       <c r="N34" t="s">
-        <v>166</v>
+        <v>30</v>
       </c>
       <c r="O34" t="s">
-        <v>166</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>177</v>
+      </c>
+      <c r="B35" t="s">
+        <v>178</v>
+      </c>
+      <c r="C35" t="s">
+        <v>179</v>
+      </c>
+      <c r="D35" t="s">
+        <v>180</v>
+      </c>
+      <c r="E35" t="s">
         <v>181</v>
       </c>
-      <c r="B35" t="s">
-        <v>166</v>
-      </c>
-      <c r="C35" t="s">
-        <v>167</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
+        <v>180</v>
+      </c>
+      <c r="G35" t="s">
+        <v>181</v>
+      </c>
+      <c r="H35" t="s">
         <v>182</v>
       </c>
-      <c r="E35" t="s">
+      <c r="I35" t="s">
         <v>183</v>
-      </c>
-      <c r="F35" t="s">
-        <v>182</v>
-      </c>
-      <c r="G35" t="s">
-        <v>183</v>
-      </c>
-      <c r="H35" t="s">
-        <v>184</v>
-      </c>
-      <c r="I35" t="s">
-        <v>185</v>
       </c>
       <c r="J35">
         <v>4</v>
@@ -2695,45 +2695,45 @@
         <v>21</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M35" t="s">
         <v>22</v>
       </c>
       <c r="N35" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="O35" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B36" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" t="s">
+        <v>179</v>
+      </c>
+      <c r="D36" t="s">
+        <v>185</v>
+      </c>
+      <c r="E36" t="s">
         <v>186</v>
       </c>
-      <c r="B36" t="s">
-        <v>166</v>
-      </c>
-      <c r="C36" t="s">
-        <v>167</v>
-      </c>
-      <c r="D36" t="s">
+      <c r="F36" t="s">
+        <v>185</v>
+      </c>
+      <c r="G36" t="s">
+        <v>186</v>
+      </c>
+      <c r="H36" t="s">
         <v>187</v>
       </c>
-      <c r="E36" t="s">
+      <c r="I36" t="s">
         <v>188</v>
-      </c>
-      <c r="F36" t="s">
-        <v>187</v>
-      </c>
-      <c r="G36" t="s">
-        <v>188</v>
-      </c>
-      <c r="H36" t="s">
-        <v>189</v>
-      </c>
-      <c r="I36" t="s">
-        <v>190</v>
       </c>
       <c r="J36">
         <v>4</v>
@@ -2742,45 +2742,45 @@
         <v>21</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M36" t="s">
         <v>22</v>
       </c>
       <c r="N36" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="O36" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>189</v>
+      </c>
+      <c r="B37" t="s">
+        <v>178</v>
+      </c>
+      <c r="C37" t="s">
+        <v>179</v>
+      </c>
+      <c r="D37" t="s">
+        <v>190</v>
+      </c>
+      <c r="E37" t="s">
+        <v>186</v>
+      </c>
+      <c r="F37" t="s">
+        <v>190</v>
+      </c>
+      <c r="G37" t="s">
+        <v>186</v>
+      </c>
+      <c r="H37" t="s">
         <v>191</v>
       </c>
-      <c r="B37" t="s">
-        <v>166</v>
-      </c>
-      <c r="C37" t="s">
-        <v>167</v>
-      </c>
-      <c r="D37" t="s">
-        <v>192</v>
-      </c>
-      <c r="E37" t="s">
-        <v>193</v>
-      </c>
-      <c r="F37" t="s">
-        <v>192</v>
-      </c>
-      <c r="G37" t="s">
-        <v>193</v>
-      </c>
-      <c r="H37" t="s">
-        <v>194</v>
-      </c>
       <c r="I37" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="J37">
         <v>4</v>
@@ -2789,157 +2789,157 @@
         <v>21</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="M37" t="s">
         <v>22</v>
       </c>
       <c r="N37" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="O37" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>192</v>
+      </c>
+      <c r="B38" t="s">
+        <v>193</v>
+      </c>
+      <c r="C38" t="s">
+        <v>194</v>
+      </c>
+      <c r="D38" t="s">
+        <v>195</v>
+      </c>
+      <c r="E38" t="s">
         <v>196</v>
       </c>
-      <c r="B38" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" t="s">
-        <v>26</v>
-      </c>
-      <c r="D38" t="s">
-        <v>197</v>
-      </c>
-      <c r="E38" t="s">
-        <v>198</v>
-      </c>
       <c r="F38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G38" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H38" t="s">
         <v>197</v>
       </c>
       <c r="I38" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K38" t="s">
         <v>21</v>
       </c>
       <c r="L38">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M38" t="s">
         <v>22</v>
       </c>
       <c r="N38" t="s">
-        <v>30</v>
+        <v>193</v>
       </c>
       <c r="O38" t="s">
-        <v>30</v>
+        <v>193</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>199</v>
+      </c>
+      <c r="B39" t="s">
+        <v>193</v>
+      </c>
+      <c r="C39" t="s">
+        <v>194</v>
+      </c>
+      <c r="D39" t="s">
         <v>200</v>
       </c>
-      <c r="B39" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" t="s">
-        <v>26</v>
-      </c>
-      <c r="D39" t="s">
-        <v>201</v>
-      </c>
       <c r="E39" t="s">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="F39" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G39" t="s">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="H39" t="s">
         <v>201</v>
       </c>
       <c r="I39" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K39" t="s">
         <v>21</v>
       </c>
       <c r="L39">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="M39" t="s">
         <v>22</v>
       </c>
       <c r="N39" t="s">
-        <v>30</v>
+        <v>193</v>
       </c>
       <c r="O39" t="s">
-        <v>30</v>
+        <v>193</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>203</v>
+      </c>
+      <c r="B40" t="s">
+        <v>193</v>
+      </c>
+      <c r="C40" t="s">
+        <v>194</v>
+      </c>
+      <c r="D40" t="s">
         <v>204</v>
       </c>
-      <c r="B40" t="s">
-        <v>25</v>
-      </c>
-      <c r="C40" t="s">
-        <v>26</v>
-      </c>
-      <c r="D40" t="s">
+      <c r="E40" t="s">
         <v>205</v>
       </c>
-      <c r="E40" t="s">
+      <c r="F40" t="s">
+        <v>204</v>
+      </c>
+      <c r="G40" t="s">
+        <v>205</v>
+      </c>
+      <c r="H40" t="s">
         <v>206</v>
-      </c>
-      <c r="F40" t="s">
-        <v>205</v>
-      </c>
-      <c r="G40" t="s">
-        <v>206</v>
-      </c>
-      <c r="H40" t="s">
-        <v>205</v>
       </c>
       <c r="I40" t="s">
         <v>207</v>
       </c>
       <c r="J40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K40" t="s">
         <v>21</v>
       </c>
       <c r="L40">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="M40" t="s">
         <v>22</v>
       </c>
       <c r="N40" t="s">
-        <v>30</v>
+        <v>193</v>
       </c>
       <c r="O40" t="s">
-        <v>30</v>
+        <v>193</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
@@ -2947,28 +2947,28 @@
         <v>208</v>
       </c>
       <c r="B41" t="s">
+        <v>193</v>
+      </c>
+      <c r="C41" t="s">
+        <v>194</v>
+      </c>
+      <c r="D41" t="s">
         <v>209</v>
       </c>
-      <c r="C41" t="s">
+      <c r="E41" t="s">
         <v>210</v>
       </c>
-      <c r="D41" t="s">
+      <c r="F41" t="s">
+        <v>209</v>
+      </c>
+      <c r="G41" t="s">
+        <v>210</v>
+      </c>
+      <c r="H41" t="s">
         <v>211</v>
       </c>
-      <c r="E41" t="s">
+      <c r="I41" t="s">
         <v>212</v>
-      </c>
-      <c r="F41" t="s">
-        <v>211</v>
-      </c>
-      <c r="G41" t="s">
-        <v>212</v>
-      </c>
-      <c r="H41" t="s">
-        <v>213</v>
-      </c>
-      <c r="I41" t="s">
-        <v>214</v>
       </c>
       <c r="J41">
         <v>4</v>
@@ -2983,39 +2983,39 @@
         <v>22</v>
       </c>
       <c r="N41" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="O41" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>213</v>
+      </c>
+      <c r="B42" t="s">
+        <v>193</v>
+      </c>
+      <c r="C42" t="s">
+        <v>194</v>
+      </c>
+      <c r="D42" t="s">
+        <v>214</v>
+      </c>
+      <c r="E42" t="s">
         <v>215</v>
       </c>
-      <c r="B42" t="s">
-        <v>209</v>
-      </c>
-      <c r="C42" t="s">
-        <v>210</v>
-      </c>
-      <c r="D42" t="s">
+      <c r="F42" t="s">
+        <v>214</v>
+      </c>
+      <c r="G42" t="s">
+        <v>215</v>
+      </c>
+      <c r="H42" t="s">
         <v>216</v>
       </c>
-      <c r="E42" t="s">
+      <c r="I42" t="s">
         <v>217</v>
-      </c>
-      <c r="F42" t="s">
-        <v>216</v>
-      </c>
-      <c r="G42" t="s">
-        <v>217</v>
-      </c>
-      <c r="H42" t="s">
-        <v>218</v>
-      </c>
-      <c r="I42" t="s">
-        <v>219</v>
       </c>
       <c r="J42">
         <v>4</v>
@@ -3030,39 +3030,39 @@
         <v>22</v>
       </c>
       <c r="N42" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="O42" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>218</v>
+      </c>
+      <c r="B43" t="s">
+        <v>193</v>
+      </c>
+      <c r="C43" t="s">
+        <v>194</v>
+      </c>
+      <c r="D43" t="s">
+        <v>219</v>
+      </c>
+      <c r="E43" t="s">
         <v>220</v>
       </c>
-      <c r="B43" t="s">
-        <v>209</v>
-      </c>
-      <c r="C43" t="s">
-        <v>210</v>
-      </c>
-      <c r="D43" t="s">
+      <c r="F43" t="s">
+        <v>219</v>
+      </c>
+      <c r="G43" t="s">
+        <v>220</v>
+      </c>
+      <c r="H43" t="s">
         <v>221</v>
       </c>
-      <c r="E43" t="s">
-        <v>217</v>
-      </c>
-      <c r="F43" t="s">
-        <v>221</v>
-      </c>
-      <c r="G43" t="s">
-        <v>217</v>
-      </c>
-      <c r="H43" t="s">
+      <c r="I43" t="s">
         <v>222</v>
-      </c>
-      <c r="I43" t="s">
-        <v>219</v>
       </c>
       <c r="J43">
         <v>4</v>
@@ -3077,10 +3077,10 @@
         <v>22</v>
       </c>
       <c r="N43" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="O43" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
